--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -9556,34 +9556,34 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
-        <v>8419000</v>
+        <v>6903000</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>29334</v>
+        <v>24052</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="5" t="n">
-        <v>6903580</v>
+        <v>6903000</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>24054</v>
+        <v>24052</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10650,38 +10650,30 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>9018000</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>23005</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K146" s="5" t="n">
+        <v>9018000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>23005</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -10690,7 +10682,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10725,7 +10717,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10787,7 +10779,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10849,7 +10841,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10911,7 +10903,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -11113,7 +11105,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -11175,7 +11167,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -11517,7 +11509,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -11649,7 +11641,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11711,7 +11703,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11773,7 +11765,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11835,7 +11827,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11897,7 +11889,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11959,7 +11951,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -12091,7 +12083,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -12153,7 +12145,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -12355,7 +12347,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12417,7 +12409,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -12479,7 +12471,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12611,7 +12603,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12673,7 +12665,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12735,7 +12727,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12797,7 +12789,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12859,7 +12851,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12921,7 +12913,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12983,7 +12975,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -13045,7 +13037,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -13107,7 +13099,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -13169,7 +13161,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13301,7 +13293,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -13363,7 +13355,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13425,7 +13417,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13557,7 +13549,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13619,7 +13611,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13681,7 +13673,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13743,7 +13735,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13805,7 +13797,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13867,7 +13859,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13929,7 +13921,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13991,7 +13983,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -14053,7 +14045,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -14115,7 +14107,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -14177,7 +14169,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -14239,7 +14231,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -14301,7 +14293,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14363,7 +14355,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14495,7 +14487,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14557,7 +14549,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14619,7 +14611,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14681,7 +14673,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14743,7 +14735,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14805,7 +14797,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14867,7 +14859,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14929,7 +14921,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14991,7 +14983,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -15053,7 +15045,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -15115,7 +15107,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -15177,7 +15169,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -15239,7 +15231,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15301,7 +15293,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15363,7 +15355,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15425,7 +15417,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15487,7 +15479,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15549,7 +15541,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15611,7 +15603,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15673,7 +15665,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15735,7 +15727,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15797,7 +15789,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -15859,7 +15851,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15921,7 +15913,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15983,7 +15975,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -16045,7 +16037,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16107,7 +16099,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16169,7 +16161,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -16231,7 +16223,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16293,7 +16285,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16355,7 +16347,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16417,7 +16409,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16479,7 +16471,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16541,7 +16533,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -16603,7 +16595,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16665,7 +16657,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16727,7 +16719,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16789,7 +16781,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16851,7 +16843,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16913,7 +16905,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16975,7 +16967,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -17037,7 +17029,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -17099,7 +17091,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -17161,7 +17153,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17223,7 +17215,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17285,7 +17277,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -17347,7 +17339,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -17409,7 +17401,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17471,7 +17463,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17533,7 +17525,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -17595,7 +17587,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17657,7 +17649,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17719,7 +17711,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17781,7 +17773,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17843,7 +17835,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17905,7 +17897,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17967,7 +17959,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18029,7 +18021,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -18091,7 +18083,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18153,7 +18145,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18215,7 +18207,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -18277,7 +18269,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -18339,7 +18331,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -18401,7 +18393,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18463,7 +18455,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18525,7 +18517,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -18587,7 +18579,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18649,7 +18641,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -18711,7 +18703,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18773,7 +18765,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18835,7 +18827,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18897,7 +18889,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18959,7 +18951,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -19021,7 +19013,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -19083,7 +19075,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19145,7 +19137,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -19207,7 +19199,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19269,7 +19261,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19331,7 +19323,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -19393,7 +19385,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -19455,7 +19447,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19517,7 +19509,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -19579,7 +19571,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19641,7 +19633,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19703,7 +19695,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19765,7 +19757,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -19827,7 +19819,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19889,7 +19881,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -19951,7 +19943,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20013,7 +20005,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -20075,7 +20067,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -20137,7 +20129,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20199,7 +20191,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20261,7 +20253,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20323,7 +20315,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20385,7 +20377,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20447,7 +20439,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -20509,7 +20501,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -20571,7 +20563,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20633,7 +20625,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20695,7 +20687,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20757,7 +20749,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -20819,7 +20811,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20881,7 +20873,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -20943,7 +20935,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -21005,7 +20997,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -21067,7 +21059,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -21129,7 +21121,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -21191,7 +21183,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -21253,7 +21245,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -21315,7 +21307,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21377,7 +21369,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -21439,7 +21431,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -21501,7 +21493,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -21563,7 +21555,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -21695,7 +21687,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -21757,7 +21749,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -21819,7 +21811,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21881,7 +21873,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21943,7 +21935,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -22005,7 +21997,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -22067,7 +22059,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -22129,7 +22121,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -22191,7 +22183,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -22253,7 +22245,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -22315,7 +22307,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22377,7 +22369,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -22439,7 +22431,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -22501,7 +22493,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -22633,7 +22625,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -22695,7 +22687,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -22757,7 +22749,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -22819,7 +22811,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22881,7 +22873,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22943,7 +22935,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23005,7 +22997,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23067,7 +23059,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -23129,7 +23121,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -23191,7 +23183,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -23253,7 +23245,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -23315,7 +23307,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -23377,7 +23369,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -23579,7 +23571,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -23641,7 +23633,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -23703,7 +23695,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -23835,7 +23827,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23897,7 +23889,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23959,7 +23951,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -24021,7 +24013,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -24083,7 +24075,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -24145,7 +24137,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -24277,7 +24269,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -24339,7 +24331,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -24541,7 +24533,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -24673,7 +24665,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -24805,7 +24797,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -24867,7 +24859,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -24929,7 +24921,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24991,7 +24983,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -25053,7 +25045,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -25115,7 +25107,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -31127,7 +31119,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -31469,7 +31461,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -31601,7 +31593,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -31663,7 +31655,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -31865,7 +31857,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -32062,38 +32054,30 @@
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H476" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I476" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="H476" s="5" t="n">
+        <v>9639000</v>
+      </c>
+      <c r="I476" s="5" t="n">
+        <v>24589</v>
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K476" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L476" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K476" s="5" t="n">
+        <v>9639000</v>
+      </c>
+      <c r="L476" s="5" t="n">
+        <v>24589</v>
       </c>
       <c r="M476" s="3" t="inlineStr">
         <is>
@@ -32102,7 +32086,7 @@
       </c>
       <c r="N476" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -32137,7 +32121,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -32409,7 +32393,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -32471,7 +32455,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -32603,7 +32587,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -32665,7 +32649,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -33077,7 +33061,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -33139,7 +33123,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -33201,7 +33185,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -33333,7 +33317,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -33395,7 +33379,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -33457,7 +33441,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -34545,7 +34529,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -34607,7 +34591,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -34669,7 +34653,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -34871,7 +34855,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
@@ -34933,7 +34917,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -34995,7 +34979,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -35057,7 +35041,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
@@ -35119,7 +35103,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -35181,7 +35165,7 @@
       </c>
       <c r="G523" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H523" s="5" t="n">
@@ -35243,7 +35227,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -35305,7 +35289,7 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
@@ -35367,7 +35351,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -35429,7 +35413,7 @@
       </c>
       <c r="G527" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H527" s="5" t="n">
@@ -35491,7 +35475,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -35553,7 +35537,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -35615,7 +35599,7 @@
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H530" s="5" t="n">
@@ -35677,7 +35661,7 @@
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H531" s="5" t="n">
@@ -35809,7 +35793,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -35871,7 +35855,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -35933,7 +35917,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -35995,7 +35979,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -36057,7 +36041,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -36119,7 +36103,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -36181,7 +36165,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -36243,7 +36227,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -36305,7 +36289,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -36367,7 +36351,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -36429,7 +36413,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -36491,7 +36475,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -36553,7 +36537,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -36615,7 +36599,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -36677,7 +36661,7 @@
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H547" s="5" t="n">
@@ -36739,7 +36723,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -36801,7 +36785,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -36863,7 +36847,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -36925,7 +36909,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -36987,7 +36971,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -37049,7 +37033,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -37111,7 +37095,7 @@
       </c>
       <c r="G554" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H554" s="5" t="n">
@@ -37173,7 +37157,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -37235,7 +37219,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -37297,7 +37281,7 @@
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H557" s="5" t="n">
@@ -37359,7 +37343,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -37421,7 +37405,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -37483,7 +37467,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -37545,7 +37529,7 @@
       </c>
       <c r="G561" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H561" s="5" t="n">
@@ -37677,7 +37661,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -37739,7 +37723,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -37801,7 +37785,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -37863,7 +37847,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -37925,7 +37909,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -37987,7 +37971,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -38049,7 +38033,7 @@
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H569" s="5" t="n">
@@ -38111,7 +38095,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
@@ -38173,7 +38157,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -38235,7 +38219,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -38297,7 +38281,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -38359,7 +38343,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -38421,7 +38405,7 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H575" s="5" t="n">
@@ -38483,7 +38467,7 @@
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H576" s="5" t="n">
@@ -38615,7 +38599,7 @@
       </c>
       <c r="G578" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H578" s="5" t="n">
@@ -38677,7 +38661,7 @@
       </c>
       <c r="G579" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H579" s="5" t="n">
@@ -38739,7 +38723,7 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H580" s="5" t="n">
@@ -38801,7 +38785,7 @@
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H581" s="5" t="n">
@@ -38863,7 +38847,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -38925,7 +38909,7 @@
       </c>
       <c r="G583" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H583" s="5" t="n">
@@ -38987,7 +38971,7 @@
       </c>
       <c r="G584" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H584" s="5" t="n">
@@ -39049,7 +39033,7 @@
       </c>
       <c r="G585" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H585" s="5" t="n">
@@ -39111,7 +39095,7 @@
       </c>
       <c r="G586" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H586" s="5" t="n">
@@ -39173,7 +39157,7 @@
       </c>
       <c r="G587" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H587" s="5" t="n">
@@ -39235,7 +39219,7 @@
       </c>
       <c r="G588" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H588" s="5" t="n">
@@ -39297,7 +39281,7 @@
       </c>
       <c r="G589" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H589" s="5" t="n">
@@ -39359,7 +39343,7 @@
       </c>
       <c r="G590" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H590" s="5" t="n">
@@ -39421,7 +39405,7 @@
       </c>
       <c r="G591" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H591" s="5" t="n">
@@ -39483,7 +39467,7 @@
       </c>
       <c r="G592" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H592" s="5" t="n">
@@ -39545,7 +39529,7 @@
       </c>
       <c r="G593" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H593" s="5" t="n">
@@ -39607,7 +39591,7 @@
       </c>
       <c r="G594" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H594" s="5" t="n">
@@ -39669,7 +39653,7 @@
       </c>
       <c r="G595" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H595" s="5" t="n">
@@ -39731,7 +39715,7 @@
       </c>
       <c r="G596" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H596" s="5" t="n">
@@ -39793,7 +39777,7 @@
       </c>
       <c r="G597" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H597" s="5" t="n">
@@ -39855,7 +39839,7 @@
       </c>
       <c r="G598" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H598" s="5" t="n">
@@ -39917,7 +39901,7 @@
       </c>
       <c r="G599" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H599" s="5" t="n">
@@ -39979,7 +39963,7 @@
       </c>
       <c r="G600" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H600" s="5" t="n">
@@ -40041,7 +40025,7 @@
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H601" s="5" t="n">
@@ -40103,7 +40087,7 @@
       </c>
       <c r="G602" s="3" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H602" s="5" t="n">
@@ -40165,7 +40149,7 @@
       </c>
       <c r="G603" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H603" s="5" t="n">
@@ -40227,7 +40211,7 @@
       </c>
       <c r="G604" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H604" s="5" t="n">
@@ -40289,7 +40273,7 @@
       </c>
       <c r="G605" s="3" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H605" s="5" t="n">
@@ -40351,7 +40335,7 @@
       </c>
       <c r="G606" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H606" s="5" t="n">
@@ -40413,7 +40397,7 @@
       </c>
       <c r="G607" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H607" s="5" t="n">
@@ -40475,7 +40459,7 @@
       </c>
       <c r="G608" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H608" s="5" t="n">
@@ -40537,7 +40521,7 @@
       </c>
       <c r="G609" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H609" s="5" t="n">
@@ -40599,7 +40583,7 @@
       </c>
       <c r="G610" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H610" s="5" t="n">
@@ -40661,7 +40645,7 @@
       </c>
       <c r="G611" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H611" s="5" t="n">
@@ -40723,7 +40707,7 @@
       </c>
       <c r="G612" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H612" s="5" t="n">
@@ -40785,7 +40769,7 @@
       </c>
       <c r="G613" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H613" s="5" t="n">
@@ -40847,7 +40831,7 @@
       </c>
       <c r="G614" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H614" s="5" t="n">
@@ -40909,7 +40893,7 @@
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H615" s="5" t="n">
@@ -40971,7 +40955,7 @@
       </c>
       <c r="G616" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H616" s="5" t="n">
@@ -41033,7 +41017,7 @@
       </c>
       <c r="G617" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H617" s="5" t="n">
@@ -41157,7 +41141,7 @@
       </c>
       <c r="G619" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H619" s="5" t="n">
@@ -41219,7 +41203,7 @@
       </c>
       <c r="G620" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H620" s="5" t="n">
@@ -41281,7 +41265,7 @@
       </c>
       <c r="G621" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H621" s="5" t="n">
@@ -41343,7 +41327,7 @@
       </c>
       <c r="G622" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H622" s="5" t="n">
@@ -41405,7 +41389,7 @@
       </c>
       <c r="G623" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H623" s="5" t="n">
@@ -41467,7 +41451,7 @@
       </c>
       <c r="G624" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H624" s="5" t="n">
@@ -41529,7 +41513,7 @@
       </c>
       <c r="G625" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H625" s="5" t="n">
@@ -41591,7 +41575,7 @@
       </c>
       <c r="G626" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H626" s="5" t="n">
@@ -41653,7 +41637,7 @@
       </c>
       <c r="G627" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H627" s="5" t="n">
@@ -41715,7 +41699,7 @@
       </c>
       <c r="G628" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H628" s="5" t="n">
@@ -41777,7 +41761,7 @@
       </c>
       <c r="G629" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H629" s="5" t="n">
@@ -41839,7 +41823,7 @@
       </c>
       <c r="G630" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H630" s="5" t="n">
@@ -41901,7 +41885,7 @@
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H631" s="5" t="n">
@@ -41963,7 +41947,7 @@
       </c>
       <c r="G632" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H632" s="5" t="n">
@@ -42025,7 +42009,7 @@
       </c>
       <c r="G633" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H633" s="5" t="n">
@@ -42087,7 +42071,7 @@
       </c>
       <c r="G634" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H634" s="5" t="n">
@@ -42149,7 +42133,7 @@
       </c>
       <c r="G635" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H635" s="5" t="n">
@@ -42211,7 +42195,7 @@
       </c>
       <c r="G636" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H636" s="5" t="n">
@@ -42343,7 +42327,7 @@
       </c>
       <c r="G638" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H638" s="5" t="n">
@@ -42405,7 +42389,7 @@
       </c>
       <c r="G639" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H639" s="5" t="n">
@@ -42467,7 +42451,7 @@
       </c>
       <c r="G640" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H640" s="5" t="n">
@@ -42529,7 +42513,7 @@
       </c>
       <c r="G641" s="3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H641" s="5" t="n">
@@ -42591,7 +42575,7 @@
       </c>
       <c r="G642" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H642" s="5" t="n">
@@ -42653,7 +42637,7 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H643" s="5" t="n">
@@ -42715,7 +42699,7 @@
       </c>
       <c r="G644" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H644" s="5" t="n">
@@ -42777,7 +42761,7 @@
       </c>
       <c r="G645" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H645" s="5" t="n">
@@ -42839,7 +42823,7 @@
       </c>
       <c r="G646" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H646" s="5" t="n">
@@ -42901,7 +42885,7 @@
       </c>
       <c r="G647" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H647" s="5" t="n">
@@ -42963,7 +42947,7 @@
       </c>
       <c r="G648" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H648" s="5" t="n">
@@ -43025,7 +43009,7 @@
       </c>
       <c r="G649" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H649" s="5" t="n">
@@ -43087,7 +43071,7 @@
       </c>
       <c r="G650" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H650" s="5" t="n">
@@ -43149,7 +43133,7 @@
       </c>
       <c r="G651" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H651" s="5" t="n">
@@ -43211,7 +43195,7 @@
       </c>
       <c r="G652" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H652" s="5" t="n">
@@ -43273,7 +43257,7 @@
       </c>
       <c r="G653" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H653" s="5" t="n">
@@ -43335,7 +43319,7 @@
       </c>
       <c r="G654" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H654" s="5" t="n">
@@ -43459,7 +43443,7 @@
       </c>
       <c r="G656" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H656" s="5" t="n">
@@ -43521,7 +43505,7 @@
       </c>
       <c r="G657" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H657" s="5" t="n">
@@ -43583,7 +43567,7 @@
       </c>
       <c r="G658" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H658" s="5" t="n">
@@ -43645,7 +43629,7 @@
       </c>
       <c r="G659" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H659" s="5" t="n">
@@ -43707,7 +43691,7 @@
       </c>
       <c r="G660" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H660" s="5" t="n">
@@ -43769,7 +43753,7 @@
       </c>
       <c r="G661" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H661" s="5" t="n">
@@ -43831,7 +43815,7 @@
       </c>
       <c r="G662" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H662" s="5" t="n">
@@ -43893,7 +43877,7 @@
       </c>
       <c r="G663" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H663" s="5" t="n">
@@ -43955,7 +43939,7 @@
       </c>
       <c r="G664" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H664" s="5" t="n">
@@ -44017,7 +44001,7 @@
       </c>
       <c r="G665" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H665" s="5" t="n">
@@ -44079,7 +44063,7 @@
       </c>
       <c r="G666" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H666" s="5" t="n">
@@ -44211,7 +44195,7 @@
       </c>
       <c r="G668" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H668" s="5" t="n">
@@ -44273,7 +44257,7 @@
       </c>
       <c r="G669" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H669" s="5" t="n">
@@ -44335,7 +44319,7 @@
       </c>
       <c r="G670" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H670" s="5" t="n">
@@ -44397,7 +44381,7 @@
       </c>
       <c r="G671" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H671" s="5" t="n">
@@ -44459,7 +44443,7 @@
       </c>
       <c r="G672" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H672" s="5" t="n">
@@ -44521,7 +44505,7 @@
       </c>
       <c r="G673" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H673" s="5" t="n">
@@ -44583,7 +44567,7 @@
       </c>
       <c r="G674" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H674" s="5" t="n">
@@ -44645,7 +44629,7 @@
       </c>
       <c r="G675" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H675" s="5" t="n">
@@ -44707,7 +44691,7 @@
       </c>
       <c r="G676" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H676" s="5" t="n">
@@ -44769,7 +44753,7 @@
       </c>
       <c r="G677" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H677" s="5" t="n">
@@ -44831,7 +44815,7 @@
       </c>
       <c r="G678" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H678" s="5" t="n">
@@ -44893,7 +44877,7 @@
       </c>
       <c r="G679" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H679" s="5" t="n">
@@ -44955,7 +44939,7 @@
       </c>
       <c r="G680" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H680" s="5" t="n">
@@ -45157,7 +45141,7 @@
       </c>
       <c r="G683" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H683" s="5" t="n">
@@ -45219,7 +45203,7 @@
       </c>
       <c r="G684" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H684" s="5" t="n">
@@ -45281,7 +45265,7 @@
       </c>
       <c r="G685" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H685" s="5" t="n">
@@ -45343,7 +45327,7 @@
       </c>
       <c r="G686" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H686" s="5" t="n">
@@ -45405,7 +45389,7 @@
       </c>
       <c r="G687" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H687" s="5" t="n">
@@ -45467,7 +45451,7 @@
       </c>
       <c r="G688" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H688" s="5" t="n">
@@ -45529,7 +45513,7 @@
       </c>
       <c r="G689" s="3" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="H689" s="5" t="n">
@@ -45591,7 +45575,7 @@
       </c>
       <c r="G690" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H690" s="5" t="n">
@@ -45653,7 +45637,7 @@
       </c>
       <c r="G691" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H691" s="5" t="n">
@@ -45715,7 +45699,7 @@
       </c>
       <c r="G692" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H692" s="5" t="n">
@@ -45777,7 +45761,7 @@
       </c>
       <c r="G693" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H693" s="5" t="n">
@@ -45839,7 +45823,7 @@
       </c>
       <c r="G694" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H694" s="5" t="n">
@@ -45901,7 +45885,7 @@
       </c>
       <c r="G695" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H695" s="5" t="n">
@@ -45963,7 +45947,7 @@
       </c>
       <c r="G696" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H696" s="5" t="n">
@@ -46095,7 +46079,7 @@
       </c>
       <c r="G698" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H698" s="5" t="n">
@@ -46157,7 +46141,7 @@
       </c>
       <c r="G699" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H699" s="5" t="n">
@@ -46219,7 +46203,7 @@
       </c>
       <c r="G700" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H700" s="5" t="n">
@@ -46281,7 +46265,7 @@
       </c>
       <c r="G701" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H701" s="5" t="n">
@@ -46343,7 +46327,7 @@
       </c>
       <c r="G702" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H702" s="5" t="n">
@@ -46405,7 +46389,7 @@
       </c>
       <c r="G703" s="3" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H703" s="5" t="n">
@@ -46467,7 +46451,7 @@
       </c>
       <c r="G704" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H704" s="5" t="n">
@@ -46529,7 +46513,7 @@
       </c>
       <c r="G705" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H705" s="5" t="n">
@@ -46591,7 +46575,7 @@
       </c>
       <c r="G706" s="3" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="H706" s="5" t="n">
@@ -46653,7 +46637,7 @@
       </c>
       <c r="G707" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H707" s="5" t="n">
@@ -46715,7 +46699,7 @@
       </c>
       <c r="G708" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H708" s="5" t="n">
@@ -46777,7 +46761,7 @@
       </c>
       <c r="G709" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H709" s="5" t="n">
@@ -46839,7 +46823,7 @@
       </c>
       <c r="G710" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H710" s="5" t="n">
@@ -47041,7 +47025,7 @@
       </c>
       <c r="G713" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H713" s="5" t="n">
@@ -47103,7 +47087,7 @@
       </c>
       <c r="G714" s="3" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H714" s="5" t="n">
@@ -47165,7 +47149,7 @@
       </c>
       <c r="G715" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H715" s="5" t="n">
@@ -47227,7 +47211,7 @@
       </c>
       <c r="G716" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H716" s="5" t="n">
@@ -47289,7 +47273,7 @@
       </c>
       <c r="G717" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H717" s="5" t="n">
@@ -47351,7 +47335,7 @@
       </c>
       <c r="G718" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H718" s="5" t="n">
@@ -47413,7 +47397,7 @@
       </c>
       <c r="G719" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H719" s="5" t="n">
@@ -47475,7 +47459,7 @@
       </c>
       <c r="G720" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H720" s="5" t="n">
@@ -47537,7 +47521,7 @@
       </c>
       <c r="G721" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H721" s="5" t="n">
@@ -47599,7 +47583,7 @@
       </c>
       <c r="G722" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H722" s="5" t="n">
@@ -47661,7 +47645,7 @@
       </c>
       <c r="G723" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H723" s="5" t="n">
@@ -47723,7 +47707,7 @@
       </c>
       <c r="G724" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H724" s="5" t="n">
@@ -47785,7 +47769,7 @@
       </c>
       <c r="G725" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H725" s="5" t="n">
@@ -47987,7 +47971,7 @@
       </c>
       <c r="G728" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H728" s="5" t="n">
@@ -48049,7 +48033,7 @@
       </c>
       <c r="G729" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H729" s="5" t="n">
@@ -48111,7 +48095,7 @@
       </c>
       <c r="G730" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H730" s="5" t="n">
@@ -48173,7 +48157,7 @@
       </c>
       <c r="G731" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H731" s="5" t="n">
@@ -48235,7 +48219,7 @@
       </c>
       <c r="G732" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H732" s="5" t="n">
@@ -48297,7 +48281,7 @@
       </c>
       <c r="G733" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H733" s="5" t="n">
@@ -48359,7 +48343,7 @@
       </c>
       <c r="G734" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H734" s="5" t="n">
@@ -48421,7 +48405,7 @@
       </c>
       <c r="G735" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H735" s="5" t="n">
@@ -48483,7 +48467,7 @@
       </c>
       <c r="G736" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H736" s="5" t="n">
@@ -48545,7 +48529,7 @@
       </c>
       <c r="G737" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H737" s="5" t="n">
@@ -48607,7 +48591,7 @@
       </c>
       <c r="G738" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H738" s="5" t="n">
@@ -48669,7 +48653,7 @@
       </c>
       <c r="G739" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H739" s="5" t="n">
@@ -48731,7 +48715,7 @@
       </c>
       <c r="G740" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H740" s="5" t="n">
@@ -49003,7 +48987,7 @@
       </c>
       <c r="G744" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H744" s="5" t="n">
@@ -49065,7 +49049,7 @@
       </c>
       <c r="G745" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H745" s="5" t="n">
@@ -49127,7 +49111,7 @@
       </c>
       <c r="G746" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H746" s="5" t="n">
@@ -49189,7 +49173,7 @@
       </c>
       <c r="G747" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H747" s="5" t="n">
@@ -49251,7 +49235,7 @@
       </c>
       <c r="G748" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H748" s="5" t="n">
@@ -49313,7 +49297,7 @@
       </c>
       <c r="G749" s="3" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H749" s="5" t="n">
@@ -49375,7 +49359,7 @@
       </c>
       <c r="G750" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H750" s="5" t="n">
@@ -49437,7 +49421,7 @@
       </c>
       <c r="G751" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H751" s="5" t="n">
@@ -49499,7 +49483,7 @@
       </c>
       <c r="G752" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H752" s="5" t="n">
@@ -49613,7 +49597,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -49623,7 +49607,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>217</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50643,7 +50627,7 @@
           <t>D | 383呎 (2房)
 $918万
 $23,979/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -50651,7 +50635,7 @@
           <t>E | 383呎 (2房)
 $921万
 $24,050/呎
-(26年-07月-02日)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -50770,7 +50754,7 @@
           <t>D | 383呎 (2房)
 $896万
 $23,394/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -50778,7 +50762,7 @@
           <t>E | 383呎 (2房)
 $899万
 $23,462/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -50786,7 +50770,7 @@
           <t>F | 262呎 (1房)
 $618万
 $23,595/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -50794,7 +50778,7 @@
           <t>G | 392呎 (2房)
 $924万
 $23,579/呎
-(26年-06月-28日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -50805,12 +50789,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>J | 287呎 (1房)
-$842万
-$29,334/呎
-(在售)</t>
+$690万
+$24,052/呎
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -50858,7 +50842,7 @@
           <t>Q | 437呎 (2房)
 $1019万
 $23,327/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
     </row>
@@ -50889,7 +50873,7 @@
           <t>C | 395呎 (2房)
 $898万
 $22,722/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -50897,7 +50881,7 @@
           <t>D | 383呎 (2房)
 $874万
 $22,825/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -50905,7 +50889,7 @@
           <t>E | 383呎 (2房)
 $877万
 $22,890/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -50913,15 +50897,15 @@
           <t>F | 262呎 (1房)
 $570万
 $21,744/呎
-(26年-02月-09日)</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
+(26年-02月-10日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
+$902万
+$23,005/呎
+(26年-07月-25日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -50937,7 +50921,7 @@
           <t>J | 287呎 (1房)
 $677万
 $23,596/呎
-(26年-07月-11日)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -50985,7 +50969,7 @@
           <t>Q | 437呎 (2房)
 $1047万
 $23,968/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
     </row>
@@ -51008,7 +50992,7 @@
           <t>B | 389呎 (2房)
 $870万
 $22,355/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -51016,7 +51000,7 @@
           <t>C | 395呎 (2房)
 $876万
 $22,167/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -51024,7 +51008,7 @@
           <t>D | 383呎 (2房)
 $853万
 $22,266/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -51032,7 +51016,7 @@
           <t>E | 383呎 (2房)
 $808万
 $21,097/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -51040,7 +51024,7 @@
           <t>F | 262呎 (1房)
 $556万
 $21,218/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -51048,7 +51032,7 @@
           <t>G | 392呎 (2房)
 $889万
 $22,668/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -51064,7 +51048,7 @@
           <t>J | 287呎 (1房)
 $671万
 $23,373/呎
-(26年-07月-08日)</t>
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -51104,7 +51088,7 @@
           <t>P | 399呎 (2房)
 $952万
 $23,867/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="P15" s="22" t="inlineStr">
@@ -51112,7 +51096,7 @@
           <t>Q | 437呎 (2房)
 $1027万
 $23,503/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -51127,7 +51111,7 @@
           <t>A | 448呎 (2房)
 $968万
 $21,616/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -51135,7 +51119,7 @@
           <t>B | 389呎 (2房)
 $820万
 $21,080/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -51143,7 +51127,7 @@
           <t>C | 395呎 (2房)
 $858万
 $21,734/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -51151,7 +51135,7 @@
           <t>D | 383呎 (2房)
 $790万
 $20,616/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -51159,7 +51143,7 @@
           <t>E | 383呎 (2房)
 $792万
 $20,681/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -51167,7 +51151,7 @@
           <t>F | 262呎 (1房)
 $545万
 $20,802/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -51175,7 +51159,7 @@
           <t>G | 392呎 (2房)
 $862万
 $22,003/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -51191,7 +51175,7 @@
           <t>J | 287呎 (1房)
 $658万
 $22,927/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -51199,7 +51183,7 @@
           <t>K | 386呎 (2房)
 $864万
 $22,370/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -51207,7 +51191,7 @@
           <t>L | 381呎 (2房)
 $852万
 $22,370/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -51231,7 +51215,7 @@
           <t>P | 399呎 (2房)
 $915万
 $22,942/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="P16" s="22" t="inlineStr">
@@ -51239,7 +51223,7 @@
           <t>Q | 437呎 (2房)
 $997万
 $22,819/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
     </row>
@@ -51254,7 +51238,7 @@
           <t>A | 448呎 (2房)
 $949万
 $21,192/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -51262,7 +51246,7 @@
           <t>B | 389呎 (2房)
 $804万
 $20,668/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -51270,7 +51254,7 @@
           <t>C | 395呎 (2房)
 $748万
 $18,927/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -51278,7 +51262,7 @@
           <t>D | 383呎 (2房)
 $746万
 $19,480/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -51286,7 +51270,7 @@
           <t>E | 383呎 (2房)
 $792万
 $20,668/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -51294,7 +51278,7 @@
           <t>F | 262呎 (1房)
 $522万
 $19,908/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -51302,7 +51286,7 @@
           <t>G | 392呎 (2房)
 $799万
 $20,372/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -51318,7 +51302,7 @@
           <t>J | 287呎 (1房)
 $645万
 $22,488/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -51326,7 +51310,7 @@
           <t>K | 386呎 (2房)
 $847万
 $21,933/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -51334,7 +51318,7 @@
           <t>L | 381呎 (2房)
 $836万
 $21,932/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -51350,7 +51334,7 @@
           <t>N | 403呎 (2房)
 $896万
 $22,241/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O17" s="22" t="inlineStr">
@@ -51358,7 +51342,7 @@
           <t>P | 399呎 (2房)
 $840万
 $21,048/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="P17" s="22" t="inlineStr">
@@ -51366,7 +51350,7 @@
           <t>Q | 437呎 (2房)
 $906万
 $20,728/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
     </row>
@@ -51381,7 +51365,7 @@
           <t>A | 448呎 (2房)
 $870万
 $19,426/呎
-(26年-01月-28日)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -51389,7 +51373,7 @@
           <t>B | 389呎 (2房)
 $736万
 $18,910/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -51397,7 +51381,7 @@
           <t>C | 395呎 (2房)
 $733万
 $18,549/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -51405,7 +51389,7 @@
           <t>D | 383呎 (2房)
 $731万
 $19,094/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -51413,7 +51397,7 @@
           <t>E | 383呎 (2房)
 $719万
 $18,773/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -51421,7 +51405,7 @@
           <t>F | 262呎 (1房)
 $512万
 $19,523/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -51429,7 +51413,7 @@
           <t>G | 392呎 (2房)
 $783万
 $19,977/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -51445,7 +51429,7 @@
           <t>J | 287呎 (1房)
 $633万
 $22,059/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -51453,7 +51437,7 @@
           <t>K | 386呎 (2房)
 $822万
 $21,288/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -51461,7 +51445,7 @@
           <t>L | 381呎 (2房)
 $811万
 $21,289/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -51469,7 +51453,7 @@
           <t>M | 395呎 (2房)
 $850万
 $21,514/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -51477,7 +51461,7 @@
           <t>N | 403呎 (2房)
 $870万
 $21,593/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="O18" s="22" t="inlineStr">
@@ -51485,7 +51469,7 @@
           <t>P | 399呎 (2房)
 $815万
 $20,436/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="P18" s="22" t="inlineStr">
@@ -51493,7 +51477,7 @@
           <t>Q | 437呎 (2房)
 $879万
 $20,124/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -51508,7 +51492,7 @@
           <t>A | 448呎 (2房)
 $878万
 $19,607/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -51516,7 +51500,7 @@
           <t>B | 389呎 (2房)
 $721万
 $18,530/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -51524,7 +51508,7 @@
           <t>C | 395呎 (2房)
 $718万
 $18,180/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -51532,7 +51516,7 @@
           <t>D | 383呎 (2房)
 $717万
 $18,713/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -51540,7 +51524,7 @@
           <t>E | 383呎 (2房)
 $705万
 $18,405/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -51548,7 +51532,7 @@
           <t>F | 262呎 (1房)
 $513万
 $19,595/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -51556,7 +51540,7 @@
           <t>G | 392呎 (2房)
 $768万
 $19,582/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -51564,7 +51548,7 @@
           <t>H | 385呎 (2房)
 $819万
 $21,275/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -51572,7 +51556,7 @@
           <t>J | 287呎 (1房)
 $611万
 $21,286/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -51580,7 +51564,7 @@
           <t>K | 386呎 (2房)
 $761万
 $19,710/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -51588,7 +51572,7 @@
           <t>L | 381呎 (2房)
 $751万
 $19,711/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -51596,7 +51580,7 @@
           <t>M | 395呎 (2房)
 $801万
 $20,286/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -51604,7 +51588,7 @@
           <t>N | 403呎 (2房)
 $790万
 $19,613/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="O19" s="22" t="inlineStr">
@@ -51612,7 +51596,7 @@
           <t>P | 399呎 (2房)
 $792万
 $19,840/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="P19" s="22" t="inlineStr">
@@ -51620,7 +51604,7 @@
           <t>Q | 437呎 (2房)
 $854万
 $19,535/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -51635,7 +51619,7 @@
           <t>A | 448呎 (2房)
 $836万
 $18,672/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -51643,7 +51627,7 @@
           <t>B | 389呎 (2房)
 $698万
 $17,931/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -51651,7 +51635,7 @@
           <t>C | 395呎 (2房)
 $695万
 $17,590/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -51659,7 +51643,7 @@
           <t>D | 383呎 (2房)
 $685万
 $17,890/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -51667,7 +51651,7 @@
           <t>E | 383呎 (2房)
 $691万
 $18,044/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -51675,7 +51659,7 @@
           <t>F | 262呎 (1房)
 $500万
 $19,095/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -51683,7 +51667,7 @@
           <t>G | 392呎 (2房)
 $743万
 $18,957/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -51691,7 +51675,7 @@
           <t>H | 385呎 (2房)
 $755万
 $19,610/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -51699,7 +51683,7 @@
           <t>J | 287呎 (1房)
 $606万
 $21,105/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -51707,7 +51691,7 @@
           <t>K | 386呎 (2房)
 $739万
 $19,137/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -51715,7 +51699,7 @@
           <t>L | 381呎 (2房)
 $729万
 $19,136/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -51723,7 +51707,7 @@
           <t>M | 395呎 (2房)
 $756万
 $19,137/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -51731,7 +51715,7 @@
           <t>N | 403呎 (2房)
 $775万
 $19,228/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="O20" s="22" t="inlineStr">
@@ -51739,7 +51723,7 @@
           <t>P | 399呎 (2房)
 $776万
 $19,449/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="P20" s="22" t="inlineStr">
@@ -51747,7 +51731,7 @@
           <t>Q | 437呎 (2房)
 $837万
 $19,153/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -51762,7 +51746,7 @@
           <t>A | 448呎 (2房)
 $832万
 $18,580/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -51770,7 +51754,7 @@
           <t>B | 389呎 (2房)
 $684万
 $17,571/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -51778,7 +51762,7 @@
           <t>C | 395呎 (2房)
 $683万
 $17,281/呎
-(25年-04月-21日)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -51786,7 +51770,7 @@
           <t>D | 383呎 (2房)
 $673万
 $17,577/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -51794,7 +51778,7 @@
           <t>E | 383呎 (2房)
 $661万
 $17,269/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -51802,7 +51786,7 @@
           <t>F | 262呎 (1房)
 $470万
 $17,958/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -51810,7 +51794,7 @@
           <t>G | 392呎 (2房)
 $730万
 $18,630/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -51818,7 +51802,7 @@
           <t>H | 385呎 (2房)
 $737万
 $19,132/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -51826,7 +51810,7 @@
           <t>J | 287呎 (1房)
 $560万
 $19,498/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -51834,7 +51818,7 @@
           <t>K | 386呎 (2房)
 $717万
 $18,580/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -51842,7 +51826,7 @@
           <t>L | 381呎 (2房)
 $708万
 $18,580/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -51850,7 +51834,7 @@
           <t>M | 395呎 (2房)
 $734万
 $18,580/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -51858,7 +51842,7 @@
           <t>N | 403呎 (2房)
 $760万
 $18,851/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="O21" s="22" t="inlineStr">
@@ -51866,7 +51850,7 @@
           <t>P | 399呎 (2房)
 $761万
 $19,068/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="P21" s="22" t="inlineStr">
@@ -51874,7 +51858,7 @@
           <t>Q | 437呎 (2房)
 $821万
 $18,778/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -51889,7 +51873,7 @@
           <t>A | 448呎 (2房)
 $808万
 $18,038/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -51897,7 +51881,7 @@
           <t>B | 389呎 (2房)
 $663万
 $17,049/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -51905,7 +51889,7 @@
           <t>C | 395呎 (2房)
 $671万
 $16,980/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -51913,7 +51897,7 @@
           <t>D | 383呎 (2房)
 $662万
 $17,274/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -51921,7 +51905,7 @@
           <t>E | 383呎 (2房)
 $642万
 $16,765/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -51929,7 +51913,7 @@
           <t>F | 262呎 (1房)
 $476万
 $18,179/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -51937,7 +51921,7 @@
           <t>G | 392呎 (2房)
 $718万
 $18,309/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -51945,7 +51929,7 @@
           <t>H | 385呎 (2房)
 $718万
 $18,662/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -51953,7 +51937,7 @@
           <t>J | 287呎 (1房)
 $555万
 $19,341/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -51961,7 +51945,7 @@
           <t>K | 386呎 (2房)
 $696万
 $18,039/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -51969,7 +51953,7 @@
           <t>L | 381呎 (2房)
 $687万
 $18,037/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -51977,7 +51961,7 @@
           <t>M | 395呎 (2房)
 $712万
 $18,038/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
@@ -51985,7 +51969,7 @@
           <t>N | 403呎 (2房)
 $745万
 $18,481/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="O22" s="22" t="inlineStr">
@@ -51993,7 +51977,7 @@
           <t>P | 399呎 (2房)
 $746万
 $18,694/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="P22" s="22" t="inlineStr">
@@ -52001,7 +51985,7 @@
           <t>Q | 437呎 (2房)
 $804万
 $18,410/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -52016,7 +52000,7 @@
           <t>A | 448呎 (2房)
 $896万
 $20,000/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -52024,7 +52008,7 @@
           <t>B | 389呎 (2房)
 $657万
 $16,879/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -52032,7 +52016,7 @@
           <t>C | 395呎 (2房)
 $659万
 $16,681/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -52040,7 +52024,7 @@
           <t>D | 383呎 (2房)
 $650万
 $16,971/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -52048,7 +52032,7 @@
           <t>E | 383呎 (2房)
 $639万
 $16,681/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -52056,7 +52040,7 @@
           <t>F | 262呎 (1房)
 $454万
 $17,347/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -52064,7 +52048,7 @@
           <t>G | 392呎 (2房)
 $705万
 $17,992/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -52072,7 +52056,7 @@
           <t>H | 385呎 (2房)
 $700万
 $18,182/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -52080,7 +52064,7 @@
           <t>J | 287呎 (1房)
 $539万
 $18,777/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -52088,10 +52072,264 @@
           <t>K | 386呎 (2房)
 $712万
 $18,451/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$762万
+$20,000/呎
+(26年-03月-04日)</t>
+        </is>
+      </c>
+      <c r="M23" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$729万
+$18,451/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="N23" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$716万
+$17,772/呎
+(25年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="O23" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$738万
+$18,509/呎
+(24年-12月-04日)</t>
+        </is>
+      </c>
+      <c r="P23" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$796万
+$18,217/呎
+(25年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$905万
+$20,201/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$654万
+$16,820/呎
+(25年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$652万
+$16,501/呎
+(25年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$674万
+$17,595/呎
+(25年-10月-14日)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$636万
+$16,601/呎
+(24年-10月-28日)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$452万
+$17,263/呎
+(24年-10月-30日)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$686万
+$17,513/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$693万
+$17,997/呎
+(25年-10月-22日)</t>
+        </is>
+      </c>
+      <c r="J24" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$534万
+$18,596/呎
+(25年-11月-25日)</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$772万
+$20,000/呎
+(26年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>L | 381呎 (2房)
+$703万
+$18,451/呎
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="M24" s="22" t="inlineStr">
+        <is>
+          <t>M | 395呎 (2房)
+$798万
+$20,203/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>N | 403呎 (2房)
+$709万
+$17,596/呎
+(25年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="O24" s="22" t="inlineStr">
+        <is>
+          <t>P | 399呎 (2房)
+$718万
+$18,003/呎
+(25年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="P24" s="22" t="inlineStr">
+        <is>
+          <t>Q | 437呎 (2房)
+$788万
+$18,034/呎
+(25年-01月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 448呎 (2房)
+$784万
+$17,509/呎
+(25年-11月-26日)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 389呎 (2房)
+$648万
+$16,656/呎
+(25年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 395呎 (2房)
+$648万
+$16,418/呎
+(25年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 383呎 (2房)
+$670万
+$17,507/呎
+(25年-09月-22日)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 383呎 (2房)
+$656万
+$17,120/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 262呎 (1房)
+$450万
+$17,172/呎
+(24年-10月-28日)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 392呎 (2房)
+$683万
+$17,426/呎
+(25年-11月-17日)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 385呎 (2房)
+$686万
+$17,816/呎
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="J25" s="22" t="inlineStr">
+        <is>
+          <t>J | 287呎 (1房)
+$528万
+$18,404/呎
+(25年-11月-17日)</t>
+        </is>
+      </c>
+      <c r="K25" s="22" t="inlineStr">
+        <is>
+          <t>K | 386呎 (2房)
+$772万
+$20,000/呎
+(26年-03月-06日)</t>
+        </is>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>L | 381呎 (2房)
 $762万
@@ -52099,266 +52337,12 @@
 (26年-03月-03日)</t>
         </is>
       </c>
-      <c r="M23" s="22" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$729万
-$18,451/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="N23" s="22" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$716万
-$17,772/呎
-(25年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="O23" s="22" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$738万
-$18,509/呎
-(24年-12月-03日)</t>
-        </is>
-      </c>
-      <c r="P23" s="22" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$796万
-$18,217/呎
-(25年-04月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$905万
-$20,201/呎
-(26年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$654万
-$16,820/呎
-(25年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$652万
-$16,501/呎
-(25年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$674万
-$17,595/呎
-(25年-10月-13日)</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$636万
-$16,601/呎
-(24年-10月-27日)</t>
-        </is>
-      </c>
-      <c r="G24" s="22" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$452万
-$17,263/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$686万
-$17,513/呎
-(25年-10月-01日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$693万
-$17,997/呎
-(25年-10月-21日)</t>
-        </is>
-      </c>
-      <c r="J24" s="22" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$534万
-$18,596/呎
-(25年-11月-24日)</t>
-        </is>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$772万
-$20,000/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="L24" s="22" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$703万
-$18,451/呎
-(26年-02月-23日)</t>
-        </is>
-      </c>
-      <c r="M24" s="22" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>M | 395呎 (2房)
 $798万
 $20,203/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="N24" s="22" t="inlineStr">
-        <is>
-          <t>N | 403呎 (2房)
-$709万
-$17,596/呎
-(25年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="O24" s="22" t="inlineStr">
-        <is>
-          <t>P | 399呎 (2房)
-$718万
-$18,003/呎
-(25年-01月-20日)</t>
-        </is>
-      </c>
-      <c r="P24" s="22" t="inlineStr">
-        <is>
-          <t>Q | 437呎 (2房)
-$788万
-$18,034/呎
-(25年-01月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="inlineStr">
-        <is>
-          <t>A | 448呎 (2房)
-$784万
-$17,509/呎
-(25年-11月-25日)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>B | 389呎 (2房)
-$648万
-$16,656/呎
-(25年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>C | 395呎 (2房)
-$648万
-$16,418/呎
-(25年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>D | 383呎 (2房)
-$670万
-$17,507/呎
-(25年-09月-21日)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>E | 383呎 (2房)
-$656万
-$17,120/呎
-(24年-11月-06日)</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="inlineStr">
-        <is>
-          <t>F | 262呎 (1房)
-$450万
-$17,172/呎
-(24年-10月-27日)</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
-        <is>
-          <t>G | 392呎 (2房)
-$683万
-$17,426/呎
-(25年-11月-16日)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>H | 385呎 (2房)
-$686万
-$17,816/呎
-(25年-11月-18日)</t>
-        </is>
-      </c>
-      <c r="J25" s="22" t="inlineStr">
-        <is>
-          <t>J | 287呎 (1房)
-$528万
-$18,404/呎
-(25年-11月-16日)</t>
-        </is>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
-        <is>
-          <t>K | 386呎 (2房)
-$772万
-$20,000/呎
-(26年-03月-05日)</t>
-        </is>
-      </c>
-      <c r="L25" s="22" t="inlineStr">
-        <is>
-          <t>L | 381呎 (2房)
-$762万
-$20,000/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="M25" s="22" t="inlineStr">
-        <is>
-          <t>M | 395呎 (2房)
-$798万
-$20,203/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -52366,7 +52350,7 @@
           <t>N | 403呎 (2房)
 $706万
 $17,506/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="O25" s="22" t="inlineStr">
@@ -52374,7 +52358,7 @@
           <t>P | 399呎 (2房)
 $715万
 $17,912/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="P25" s="22" t="inlineStr">
@@ -52382,7 +52366,7 @@
           <t>Q | 437呎 (2房)
 $769万
 $17,593/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -52397,7 +52381,7 @@
           <t>A | 448呎 (2房)
 $780万
 $17,420/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -52405,7 +52389,7 @@
           <t>B | 389呎 (2房)
 $645万
 $16,571/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -52413,7 +52397,7 @@
           <t>C | 395呎 (2房)
 $645万
 $16,337/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -52421,7 +52405,7 @@
           <t>D | 383呎 (2房)
 $667万
 $17,420/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -52429,7 +52413,7 @@
           <t>E | 383呎 (2房)
 $652万
 $17,034/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -52437,7 +52421,7 @@
           <t>F | 262呎 (1房)
 $464万
 $17,714/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -52445,7 +52429,7 @@
           <t>G | 392呎 (2房)
 $680万
 $17,339/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -52453,7 +52437,7 @@
           <t>H | 385呎 (2房)
 $682万
 $17,727/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -52461,7 +52445,7 @@
           <t>J | 287呎 (1房)
 $523万
 $18,223/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -52469,7 +52453,7 @@
           <t>K | 386呎 (2房)
 $733万
 $19,000/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -52477,7 +52461,7 @@
           <t>L | 381呎 (2房)
 $686万
 $18,000/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -52493,7 +52477,7 @@
           <t>N | 403呎 (2房)
 $725万
 $18,000/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="O26" s="22" t="inlineStr">
@@ -52501,7 +52485,7 @@
           <t>P | 399呎 (2房)
 $698万
 $17,504/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="P26" s="22" t="inlineStr">
@@ -52509,7 +52493,7 @@
           <t>Q | 437呎 (2房)
 $765万
 $17,503/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -52524,7 +52508,7 @@
           <t>A | 448呎 (2房)
 $777万
 $17,335/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -52532,7 +52516,7 @@
           <t>B | 389呎 (2房)
 $641万
 $16,488/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -52540,7 +52524,7 @@
           <t>C | 395呎 (2房)
 $642万
 $16,253/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -52548,7 +52532,7 @@
           <t>D | 383呎 (2房)
 $664万
 $17,334/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -52556,7 +52540,7 @@
           <t>E | 383呎 (2房)
 $636万
 $16,619/呎
-(25年-01月-22日)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -52564,7 +52548,7 @@
           <t>F | 262呎 (1房)
 $446万
 $17,004/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -52572,7 +52556,7 @@
           <t>G | 392呎 (2房)
 $676万
 $17,253/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -52580,7 +52564,7 @@
           <t>H | 385呎 (2房)
 $770万
 $20,000/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -52588,7 +52572,7 @@
           <t>J | 287呎 (1房)
 $533万
 $18,568/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -52596,7 +52580,7 @@
           <t>K | 386呎 (2房)
 $772万
 $20,000/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -52604,7 +52588,7 @@
           <t>L | 381呎 (2房)
 $724万
 $19,000/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -52620,7 +52604,7 @@
           <t>N | 403呎 (2房)
 $725万
 $18,000/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="O27" s="22" t="inlineStr">
@@ -52628,7 +52612,7 @@
           <t>P | 399呎 (2房)
 $695万
 $17,416/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="P27" s="22" t="inlineStr">
@@ -52636,7 +52620,7 @@
           <t>Q | 437呎 (2房)
 $761万
 $17,416/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -52659,7 +52643,7 @@
           <t>B | 390呎 (2房)
 $675万
 $17,297/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -52667,7 +52651,7 @@
           <t>C | 395呎 (2房)
 $674万
 $17,053/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -52675,7 +52659,7 @@
           <t>D | 383呎 (2房)
 $663万
 $17,300/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -52683,7 +52667,7 @@
           <t>E | 384呎 (2房)
 $650万
 $16,917/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -52691,7 +52675,7 @@
           <t>F | 262呎 (1房)
 $438万
 $16,721/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -52699,7 +52683,7 @@
           <t>G | 392呎 (2房)
 $706万
 $18,000/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -52715,7 +52699,7 @@
           <t>J | 287呎 (1房)
 $530万
 $18,474/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -52723,7 +52707,7 @@
           <t>K | 387呎 (2房)
 $716万
 $18,501/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -52731,7 +52715,7 @@
           <t>L | 381呎 (2房)
 $705万
 $18,501/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -52755,7 +52739,7 @@
           <t>P | 399呎 (2房)
 $738万
 $18,501/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="P28" s="22" t="inlineStr">
@@ -52763,7 +52747,7 @@
           <t>Q | 437呎 (2房)
 $757万
 $17,330/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
     </row>
@@ -52786,7 +52770,7 @@
           <t>B | 390呎 (2房)
 $659万
 $16,903/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -52794,7 +52778,7 @@
           <t>C | 395呎 (2房)
 $668万
 $16,904/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -52802,7 +52786,7 @@
           <t>D | 383呎 (2房)
 $647万
 $16,903/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -52810,7 +52794,7 @@
           <t>E | 384呎 (2房)
 $636万
 $16,565/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -52818,7 +52802,7 @@
           <t>F | 262呎 (1房)
 $454万
 $17,321/呎
-(24年-11月-12日)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -52826,7 +52810,7 @@
           <t>G | 392呎 (2房)
 $706万
 $18,000/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -52842,7 +52826,7 @@
           <t>J | 287呎 (1房)
 $543万
 $18,923/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -52858,7 +52842,7 @@
           <t>L | 381呎 (2房)
 $770万
 $20,202/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -52882,7 +52866,7 @@
           <t>P | 399呎 (2房)
 $806万
 $20,201/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="P29" s="22" t="inlineStr">
@@ -52890,7 +52874,7 @@
           <t>Q | 437呎 (2房)
 $883万
 $20,201/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -52977,7 +52961,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -52987,7 +52971,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -53729,7 +53713,7 @@
           <t>A | 451呎 (2房)
 $1136万
 $25,177/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -53769,7 +53753,7 @@
           <t>F | 262呎 (1房)
 $672万
 $25,656/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -53856,7 +53840,7 @@
           <t>A | 451呎 (2房)
 $1108万
 $24,561/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -53864,7 +53848,7 @@
           <t>B | 383呎 (2房)
 $954万
 $24,903/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -53896,15 +53880,15 @@
           <t>F | 262呎 (1房)
 $656万
 $25,031/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>G | 392呎 (2房)
-招标单位
--
-(在售)</t>
+$964万
+$24,589/呎
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -53928,7 +53912,7 @@
           <t>K | 393呎 (2房)
 $961万
 $24,458/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -53952,7 +53936,7 @@
           <t>N | 383呎 (2房)
 $866万
 $22,608/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="O11" s="22" t="inlineStr">
@@ -53960,7 +53944,7 @@
           <t>P | 383呎 (2房)
 $882万
 $23,037/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -53983,7 +53967,7 @@
           <t>A | 451呎 (2房)
 $1081万
 $23,962/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -53991,7 +53975,7 @@
           <t>B | 383呎 (2房)
 $930万
 $24,295/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -53999,7 +53983,7 @@
           <t>C | 392呎 (2房)
 $899万
 $22,931/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -54015,7 +53999,7 @@
           <t>E | 383呎 (2房)
 $927万
 $24,211/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -54023,7 +54007,7 @@
           <t>F | 262呎 (1房)
 $640万
 $24,420/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -54031,7 +54015,7 @@
           <t>G | 392呎 (2房)
 $888万
 $22,663/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -54079,7 +54063,7 @@
           <t>N | 383呎 (2房)
 $849万
 $22,167/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="O12" s="22" t="inlineStr">
@@ -54087,7 +54071,7 @@
           <t>P | 383呎 (2房)
 $865万
 $22,587/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -54237,7 +54221,7 @@
           <t>A | 451呎 (2房)
 $972万
 $21,545/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -54245,7 +54229,7 @@
           <t>B | 383呎 (2房)
 $822万
 $21,449/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -54253,7 +54237,7 @@
           <t>C | 392呎 (2房)
 $830万
 $21,186/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -54261,7 +54245,7 @@
           <t>D | 396呎 (2房)
 $880万
 $22,220/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -54269,7 +54253,7 @@
           <t>E | 383呎 (2房)
 $826万
 $21,569/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -54277,7 +54261,7 @@
           <t>F | 262呎 (1房)
 $572万
 $21,813/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -54285,7 +54269,7 @@
           <t>G | 392呎 (2房)
 $837万
 $21,362/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -54293,7 +54277,7 @@
           <t>H | 385呎 (2房)
 $830万
 $21,564/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -54301,7 +54285,7 @@
           <t>J | 283呎 (1房)
 $655万
 $23,145/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
@@ -54309,7 +54293,7 @@
           <t>K | 393呎 (2房)
 $880万
 $22,384/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -54333,7 +54317,7 @@
           <t>N | 383呎 (2房)
 $771万
 $20,125/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="O14" s="22" t="inlineStr">
@@ -54341,7 +54325,7 @@
           <t>P | 383呎 (2房)
 $785万
 $20,504/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="P14" s="22" t="inlineStr">
@@ -54349,7 +54333,7 @@
           <t>Q | 443呎 (2房)
 $962万
 $21,725/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -54364,7 +54348,7 @@
           <t>A | 451呎 (2房)
 $948万
 $21,022/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -54372,7 +54356,7 @@
           <t>B | 383呎 (2房)
 $817万
 $21,334/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -54380,7 +54364,7 @@
           <t>C | 392呎 (2房)
 $806万
 $20,569/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -54388,7 +54372,7 @@
           <t>D | 396呎 (2房)
 $858万
 $21,679/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -54396,7 +54380,7 @@
           <t>E | 383呎 (2房)
 $806万
 $21,044/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -54404,7 +54388,7 @@
           <t>F | 262呎 (1房)
 $561万
 $21,420/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -54412,7 +54396,7 @@
           <t>G | 392呎 (2房)
 $817万
 $20,842/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -54420,7 +54404,7 @@
           <t>H | 385呎 (2房)
 $871万
 $22,613/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -54428,7 +54412,7 @@
           <t>J | 283呎 (1房)
 $649万
 $22,933/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -54436,7 +54420,7 @@
           <t>K | 393呎 (2房)
 $814万
 $20,725/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -54452,7 +54436,7 @@
           <t>M | 397呎 (2房)
 $783万
 $19,718/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -54460,7 +54444,7 @@
           <t>N | 383呎 (2房)
 $707万
 $18,460/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="O15" s="22" t="inlineStr">
@@ -54468,7 +54452,7 @@
           <t>P | 383呎 (2房)
 $720万
 $18,809/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="P15" s="22" t="inlineStr">
@@ -54476,7 +54460,7 @@
           <t>Q | 443呎 (2房)
 $944万
 $21,298/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -54491,7 +54475,7 @@
           <t>A | 451呎 (2房)
 $909万
 $20,162/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -54499,7 +54483,7 @@
           <t>B | 383呎 (2房)
 $793万
 $20,713/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -54507,7 +54491,7 @@
           <t>C | 392呎 (2房)
 $764万
 $19,485/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -54515,7 +54499,7 @@
           <t>D | 396呎 (2房)
 $787万
 $19,864/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -54523,7 +54507,7 @@
           <t>E | 383呎 (2房)
 $806万
 $21,034/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -54531,7 +54515,7 @@
           <t>F | 262呎 (1房)
 $559万
 $21,344/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -54539,7 +54523,7 @@
           <t>G | 392呎 (2房)
 $744万
 $18,972/呎
-(25年-08月-06日)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -54547,7 +54531,7 @@
           <t>H | 385呎 (2房)
 $849万
 $22,062/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -54555,7 +54539,7 @@
           <t>J | 283呎 (1房)
 $626万
 $22,134/呎
-(26年-03月-15日)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -54563,7 +54547,7 @@
           <t>K | 393呎 (2房)
 $799万
 $20,321/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -54571,7 +54555,7 @@
           <t>L | 409呎 (2房)
 $823万
 $20,125/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -54579,7 +54563,7 @@
           <t>M | 397呎 (2房)
 $817万
 $20,574/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -54587,7 +54571,7 @@
           <t>N | 383呎 (2房)
 $693万
 $18,099/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="O16" s="22" t="inlineStr">
@@ -54595,7 +54579,7 @@
           <t>P | 383呎 (2房)
 $719万
 $18,781/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="P16" s="22" t="inlineStr">
@@ -54603,7 +54587,7 @@
           <t>Q | 443呎 (2房)
 $874万
 $19,720/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -54618,7 +54602,7 @@
           <t>A | 451呎 (2房)
 $904万
 $20,055/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -54626,7 +54610,7 @@
           <t>B | 383呎 (2房)
 $770万
 $20,107/呎
-(24年-11月-14日)</t>
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -54634,7 +54618,7 @@
           <t>C | 392呎 (2房)
 $755万
 $19,270/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -54642,7 +54626,7 @@
           <t>D | 396呎 (2房)
 $783万
 $19,763/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -54650,7 +54634,7 @@
           <t>E | 383呎 (2房)
 $792万
 $20,668/呎
-(25年-03月-11日)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -54658,7 +54642,7 @@
           <t>F | 262呎 (1房)
 $497万
 $18,958/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -54666,7 +54650,7 @@
           <t>G | 392呎 (2房)
 $731万
 $18,645/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -54674,7 +54658,7 @@
           <t>H | 385呎 (2房)
 $797万
 $20,706/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -54682,7 +54666,7 @@
           <t>J | 283呎 (1房)
 $614万
 $21,710/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -54690,7 +54674,7 @@
           <t>K | 393呎 (2房)
 $783万
 $19,921/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -54706,7 +54690,7 @@
           <t>M | 397呎 (2房)
 $760万
 $19,136/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -54714,7 +54698,7 @@
           <t>N | 383呎 (2房)
 $688万
 $17,961/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="O17" s="22" t="inlineStr">
@@ -54722,7 +54706,7 @@
           <t>P | 383呎 (2房)
 $705万
 $18,410/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="P17" s="22" t="inlineStr">
@@ -54730,7 +54714,7 @@
           <t>Q | 443呎 (2房)
 $856万
 $19,334/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -54745,7 +54729,7 @@
           <t>A | 451呎 (2房)
 $895万
 $19,854/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -54753,7 +54737,7 @@
           <t>B | 383呎 (2房)
 $787万
 $20,538/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -54761,7 +54745,7 @@
           <t>C | 392呎 (2房)
 $751万
 $19,153/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -54769,7 +54753,7 @@
           <t>D | 396呎 (2房)
 $773万
 $19,525/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -54777,7 +54761,7 @@
           <t>E | 383呎 (2房)
 $699万
 $18,253/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -54785,7 +54769,7 @@
           <t>F | 262呎 (1房)
 $487万
 $18,584/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -54793,7 +54777,7 @@
           <t>G | 392呎 (2房)
 $729万
 $18,589/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -54801,7 +54785,7 @@
           <t>H | 385呎 (2房)
 $778万
 $20,197/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -54809,7 +54793,7 @@
           <t>J | 283呎 (1房)
 $573万
 $20,233/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -54817,7 +54801,7 @@
           <t>K | 393呎 (2房)
 $768万
 $19,532/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -54833,7 +54817,7 @@
           <t>M | 397呎 (2房)
 $748万
 $18,854/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -54841,7 +54825,7 @@
           <t>N | 383呎 (2房)
 $700万
 $18,279/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="O18" s="22" t="inlineStr">
@@ -54849,7 +54833,7 @@
           <t>P | 383呎 (2房)
 $679万
 $17,726/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="P18" s="22" t="inlineStr">
@@ -54857,7 +54841,7 @@
           <t>Q | 443呎 (2房)
 $840万
 $18,953/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -54872,7 +54856,7 @@
           <t>A | 451呎 (2房)
 $892万
 $19,772/呎
-(25年-11月-30日)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -54880,7 +54864,7 @@
           <t>B | 383呎 (2房)
 $723万
 $18,867/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -54888,7 +54872,7 @@
           <t>C | 392呎 (2房)
 $736万
 $18,768/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -54896,7 +54880,7 @@
           <t>D | 396呎 (2房)
 $769万
 $19,417/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -54904,7 +54888,7 @@
           <t>E | 383呎 (2房)
 $685万
 $17,893/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -54912,7 +54896,7 @@
           <t>F | 262呎 (1房)
 $477万
 $18,214/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -54920,7 +54904,7 @@
           <t>G | 392呎 (2房)
 $714万
 $18,227/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -54928,7 +54912,7 @@
           <t>H | 385呎 (2房)
 $726万
 $18,852/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -54936,7 +54920,7 @@
           <t>J | 283呎 (1房)
 $542万
 $19,152/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -54944,7 +54928,7 @@
           <t>K | 393呎 (2房)
 $752万
 $19,148/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -54952,7 +54936,7 @@
           <t>L | 409呎 (2房)
 $821万
 $20,081/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -54960,7 +54944,7 @@
           <t>M | 397呎 (2房)
 $738万
 $18,577/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -54968,7 +54952,7 @@
           <t>N | 383呎 (2房)
 $664万
 $17,342/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="O19" s="22" t="inlineStr">
@@ -54976,7 +54960,7 @@
           <t>P | 383呎 (2房)
 $688万
 $17,977/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="P19" s="22" t="inlineStr">
@@ -54984,7 +54968,7 @@
           <t>Q | 443呎 (2房)
 $779万
 $17,580/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -54999,7 +54983,7 @@
           <t>A | 451呎 (2房)
 $927万
 $20,554/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -55007,7 +54991,7 @@
           <t>B | 383呎 (2房)
 $708万
 $18,499/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -55015,7 +54999,7 @@
           <t>C | 392呎 (2房)
 $721万
 $18,393/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -55023,7 +55007,7 @@
           <t>D | 396呎 (2房)
 $766万
 $19,333/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -55031,7 +55015,7 @@
           <t>E | 383呎 (2房)
 $672万
 $17,540/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -55039,7 +55023,7 @@
           <t>F | 262呎 (1房)
 $468万
 $17,859/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -55047,7 +55031,7 @@
           <t>G | 392呎 (2房)
 $700万
 $17,870/呎
-(24年-10月-29日)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -55055,7 +55039,7 @@
           <t>H | 385呎 (2房)
 $720万
 $18,709/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -55063,7 +55047,7 @@
           <t>J | 283呎 (1房)
 $531万
 $18,777/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -55071,7 +55055,7 @@
           <t>K | 393呎 (2房)
 $738万
 $18,771/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -55079,7 +55063,7 @@
           <t>L | 409呎 (2房)
 $760万
 $18,592/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -55087,7 +55071,7 @@
           <t>M | 397呎 (2房)
 $727万
 $18,302/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -55095,7 +55079,7 @@
           <t>N | 383呎 (2房)
 $654万
 $17,086/呎
-(24年-12月-09日)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="O20" s="22" t="inlineStr">
@@ -55103,7 +55087,7 @@
           <t>P | 383呎 (2房)
 $666万
 $17,376/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="P20" s="22" t="inlineStr">
@@ -55111,7 +55095,7 @@
           <t>Q | 443呎 (2房)
 $771万
 $17,406/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -55126,7 +55110,7 @@
           <t>A | 451呎 (2房)
 $853万
 $18,914/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -55134,7 +55118,7 @@
           <t>B | 383呎 (2房)
 $692万
 $18,063/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -55142,7 +55126,7 @@
           <t>C | 392呎 (2房)
 $707万
 $18,028/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -55150,7 +55134,7 @@
           <t>D | 396呎 (2房)
 $722万
 $18,242/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -55158,7 +55142,7 @@
           <t>E | 383呎 (2房)
 $659万
 $17,196/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -55166,7 +55150,7 @@
           <t>F | 262呎 (1房)
 $459万
 $17,504/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -55174,7 +55158,7 @@
           <t>G | 392呎 (2房)
 $715万
 $18,247/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -55182,7 +55166,7 @@
           <t>H | 385呎 (2房)
 $715万
 $18,564/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -55190,7 +55174,7 @@
           <t>J | 283呎 (1房)
 $527万
 $18,629/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -55198,7 +55182,7 @@
           <t>K | 393呎 (2房)
 $723万
 $18,405/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -55206,7 +55190,7 @@
           <t>L | 409呎 (2房)
 $746万
 $18,227/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -55214,7 +55198,7 @@
           <t>M | 397呎 (2房)
 $716万
 $18,030/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -55222,7 +55206,7 @@
           <t>N | 383呎 (2房)
 $648万
 $16,916/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="O21" s="22" t="inlineStr">
@@ -55230,7 +55214,7 @@
           <t>P | 383呎 (2房)
 $659万
 $17,201/呎
-(24年-11月-26日)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="P21" s="24" t="inlineStr">
@@ -55253,7 +55237,7 @@
           <t>A | 451呎 (2房)
 $835万
 $18,508/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -55261,7 +55245,7 @@
           <t>B | 383呎 (2房)
 $668万
 $17,436/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -55269,7 +55253,7 @@
           <t>C | 392呎 (2房)
 $692万
 $17,666/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -55277,7 +55261,7 @@
           <t>D | 396呎 (2房)
 $701万
 $17,707/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -55285,7 +55269,7 @@
           <t>E | 383呎 (2房)
 $667万
 $17,407/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -55293,7 +55277,7 @@
           <t>F | 262呎 (1房)
 $445万
 $16,989/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -55301,7 +55285,7 @@
           <t>G | 392呎 (2房)
 $673万
 $17,173/呎
-(24年-11月-10日)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -55309,7 +55293,7 @@
           <t>H | 385呎 (2房)
 $710万
 $18,444/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -55317,7 +55301,7 @@
           <t>J | 283呎 (1房)
 $524万
 $18,523/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -55325,7 +55309,7 @@
           <t>K | 393呎 (2房)
 $709万
 $18,043/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -55341,7 +55325,7 @@
           <t>M | 397呎 (2房)
 $705万
 $17,763/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
@@ -55349,7 +55333,7 @@
           <t>N | 383呎 (2房)
 $641万
 $16,747/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="O22" s="22" t="inlineStr">
@@ -55357,7 +55341,7 @@
           <t>P | 383呎 (2房)
 $652万
 $17,031/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="P22" s="22" t="inlineStr">
@@ -55365,7 +55349,7 @@
           <t>Q | 443呎 (2房)
 $741万
 $16,722/呎
-(25年-06月-25日)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -55380,7 +55364,7 @@
           <t>A | 451呎 (2房)
 $802万
 $17,776/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -55388,7 +55372,7 @@
           <t>B | 383呎 (2房)
 $664万
 $17,350/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -55396,7 +55380,7 @@
           <t>C | 392呎 (2房)
 $656万
 $16,724/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -55404,7 +55388,7 @@
           <t>D | 396呎 (2房)
 $693万
 $17,497/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -55412,7 +55396,7 @@
           <t>E | 383呎 (2房)
 $636万
 $16,608/呎
-(24年-10月-21日)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -55420,7 +55404,7 @@
           <t>F | 262呎 (1房)
 $443万
 $16,905/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -55428,7 +55412,7 @@
           <t>G | 392呎 (2房)
 $670万
 $17,089/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr">
@@ -55444,7 +55428,7 @@
           <t>J | 283呎 (1房)
 $486万
 $17,166/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -55452,7 +55436,7 @@
           <t>K | 393呎 (2房)
 $688万
 $17,517/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -55460,7 +55444,7 @@
           <t>L | 409呎 (2房)
 $710万
 $17,350/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -55468,7 +55452,7 @@
           <t>M | 397呎 (2房)
 $685万
 $17,247/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -55476,7 +55460,7 @@
           <t>N | 383呎 (2房)
 $635万
 $16,582/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="O23" s="22" t="inlineStr">
@@ -55484,7 +55468,7 @@
           <t>P | 383呎 (2房)
 $643万
 $16,789/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="P23" s="22" t="inlineStr">
@@ -55492,7 +55476,7 @@
           <t>Q | 443呎 (2房)
 $734万
 $16,558/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -55507,7 +55491,7 @@
           <t>A | 451呎 (2房)
 $784万
 $17,379/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -55515,7 +55499,7 @@
           <t>B | 383呎 (2房)
 $685万
 $17,896/呎
-(24年-11月-11日)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -55523,7 +55507,7 @@
           <t>C | 392呎 (2房)
 $665万
 $16,969/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -55531,7 +55515,7 @@
           <t>D | 396呎 (2房)
 $673万
 $17,005/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -55539,7 +55523,7 @@
           <t>E | 383呎 (2房)
 $633万
 $16,527/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -55547,7 +55531,7 @@
           <t>F | 262呎 (1房)
 $441万
 $16,821/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -55555,7 +55539,7 @@
           <t>G | 392呎 (2房)
 $667万
 $17,005/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -55563,7 +55547,7 @@
           <t>H | 385呎 (2房)
 $639万
 $16,608/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -55571,7 +55555,7 @@
           <t>J | 283呎 (1房)
 $472万
 $16,664/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -55579,7 +55563,7 @@
           <t>K | 394呎 (2房)
 $687万
 $17,429/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -55595,7 +55579,7 @@
           <t>M | 397呎 (2房)
 $683万
 $17,194/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="N24" s="22" t="inlineStr">
@@ -55603,7 +55587,7 @@
           <t>N | 383呎 (2房)
 $648万
 $16,906/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
       <c r="O24" s="22" t="inlineStr">
@@ -55611,7 +55595,7 @@
           <t>P | 383呎 (2房)
 $646万
 $16,864/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="P24" s="22" t="inlineStr">
@@ -55619,7 +55603,7 @@
           <t>Q | 443呎 (2房)
 $732万
 $16,533/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -55634,7 +55618,7 @@
           <t>A | 451呎 (2房)
 $761万
 $16,882/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -55642,7 +55626,7 @@
           <t>B | 383呎 (2房)
 $669万
 $17,473/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -55650,7 +55634,7 @@
           <t>C | 392呎 (2房)
 $649万
 $16,559/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -55658,7 +55642,7 @@
           <t>D | 396呎 (2房)
 $657万
 $16,598/呎
-(25年-01月-06日)</t>
+(25年-01月-07日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -55666,7 +55650,7 @@
           <t>E | 383呎 (2房)
 $630万
 $16,444/呎
-(24年-10月-21日)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -55674,7 +55658,7 @@
           <t>F | 262呎 (1房)
 $441万
 $16,844/呎
-(24年-11月-05日)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -55682,7 +55666,7 @@
           <t>G | 392呎 (2房)
 $650万
 $16,594/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -55690,7 +55674,7 @@
           <t>H | 385呎 (2房)
 $636万
 $16,527/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -55698,7 +55682,7 @@
           <t>J | 283呎 (1房)
 $469万
 $16,580/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -55706,7 +55690,7 @@
           <t>K | 394呎 (2房)
 $683万
 $17,343/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -55730,7 +55714,7 @@
           <t>N | 383呎 (2房)
 $654万
 $17,089/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="O25" s="22" t="inlineStr">
@@ -55738,7 +55722,7 @@
           <t>P | 383呎 (2房)
 $631万
 $16,486/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="P25" s="22" t="inlineStr">
@@ -55746,7 +55730,7 @@
           <t>Q | 443呎 (2房)
 $730万
 $16,483/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -55761,7 +55745,7 @@
           <t>A | 451呎 (2房)
 $754万
 $16,712/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -55769,7 +55753,7 @@
           <t>B | 383呎 (2房)
 $666万
 $17,384/呎
-(25年-05月-08日)</t>
+(25年-05月-09日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -55777,7 +55761,7 @@
           <t>C | 392呎 (2房)
 $646万
 $16,474/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -55785,7 +55769,7 @@
           <t>D | 396呎 (2房)
 $654万
 $16,513/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -55793,7 +55777,7 @@
           <t>E | 383呎 (2房)
 $627万
 $16,360/呎
-(24年-10月-30日)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -55801,7 +55785,7 @@
           <t>F | 262呎 (1房)
 $436万
 $16,656/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -55809,7 +55793,7 @@
           <t>G | 392呎 (2房)
 $647万
 $16,508/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -55817,7 +55801,7 @@
           <t>H | 385呎 (2房)
 $633万
 $16,444/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -55825,7 +55809,7 @@
           <t>J | 283呎 (1房)
 $467万
 $16,498/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -55833,7 +55817,7 @@
           <t>K | 394呎 (2房)
 $680万
 $17,256/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -55849,7 +55833,7 @@
           <t>M | 397呎 (2房)
 $715万
 $18,000/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
@@ -55857,7 +55841,7 @@
           <t>N | 383呎 (2房)
 $640万
 $16,700/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="O26" s="22" t="inlineStr">
@@ -55865,7 +55849,7 @@
           <t>P | 383呎 (2房)
 $629万
 $16,433/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="P26" s="22" t="inlineStr">
@@ -55873,7 +55857,7 @@
           <t>Q | 443呎 (2房)
 $728万
 $16,436/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -55888,7 +55872,7 @@
           <t>A | 451呎 (2房)
 $747万
 $16,554/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -55896,7 +55880,7 @@
           <t>B | 383呎 (2房)
 $662万
 $17,298/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -55904,7 +55888,7 @@
           <t>C | 392呎 (2房)
 $829万
 $21,148/呎
-(26年-07月-04日)</t>
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -55912,7 +55896,7 @@
           <t>D | 396呎 (2房)
 $651万
 $16,429/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -55920,7 +55904,7 @@
           <t>E | 383呎 (2房)
 $811万
 $21,164/呎
-(26年-06月-29日)</t>
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -55928,7 +55912,7 @@
           <t>F | 262呎 (1房)
 $434万
 $16,573/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -55936,7 +55920,7 @@
           <t>G | 392呎 (2房)
 $644万
 $16,426/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -55944,7 +55928,7 @@
           <t>H | 385呎 (2房)
 $656万
 $17,039/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -55952,7 +55936,7 @@
           <t>J | 283呎 (1房)
 $484万
 $17,120/呎
-(24年-12月-16日)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -55960,7 +55944,7 @@
           <t>K | 394呎 (2房)
 $677万
 $17,173/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -55984,7 +55968,7 @@
           <t>N | 383呎 (2房)
 $638万
 $16,650/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="O27" s="22" t="inlineStr">
@@ -55992,7 +55976,7 @@
           <t>P | 383呎 (2房)
 $615万
 $16,050/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="P27" s="22" t="inlineStr">
@@ -56000,7 +55984,7 @@
           <t>Q | 443呎 (2房)
 $726万
 $16,386/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
     </row>
@@ -56015,7 +55999,7 @@
           <t>A | 450呎 (2房)
 $744万
 $16,538/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -56023,7 +56007,7 @@
           <t>B | 383呎 (2房)
 $648万
 $16,924/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -56031,7 +56015,7 @@
           <t>C | 392呎 (2房)
 $639万
 $16,309/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -56039,7 +56023,7 @@
           <t>D | 396呎 (2房)
 $649万
 $16,394/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -56047,7 +56031,7 @@
           <t>E | 383呎 (2房)
 $622万
 $16,245/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -56055,7 +56039,7 @@
           <t>F | 262呎 (1房)
 $425万
 $16,210/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -56063,7 +56047,7 @@
           <t>G | 392呎 (2房)
 $642万
 $16,390/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -56071,7 +56055,7 @@
           <t>H | 385呎 (2房)
 $640万
 $16,618/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -56079,7 +56063,7 @@
           <t>J | 283呎 (1房)
 $482万
 $17,032/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -56087,7 +56071,7 @@
           <t>K | 394呎 (2房)
 $709万
 $18,000/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -56111,7 +56095,7 @@
           <t>N | 383呎 (2房)
 $636万
 $16,601/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="O28" s="22" t="inlineStr">
@@ -56119,7 +56103,7 @@
           <t>P | 383呎 (2房)
 $636万
 $16,601/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="P28" s="22" t="inlineStr">
@@ -56127,7 +56111,7 @@
           <t>Q | 443呎 (2房)
 $724万
 $16,336/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -56142,7 +56126,7 @@
           <t>A | 450呎 (2房)
 $741万
 $16,467/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -56150,7 +56134,7 @@
           <t>B | 383呎 (2房)
 $627万
 $16,371/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -56158,7 +56142,7 @@
           <t>C | 392呎 (2房)
 $634万
 $16,176/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -56166,7 +56150,7 @@
           <t>D | 396呎 (2房)
 $661万
 $16,702/呎
-(25年-01月-02日)</t>
+(25年-01月-03日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -56174,7 +56158,7 @@
           <t>E | 383呎 (2房)
 $624万
 $16,303/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -56182,7 +56166,7 @@
           <t>F | 262呎 (1房)
 $424万
 $16,202/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -56190,7 +56174,7 @@
           <t>G | 392呎 (2房)
 $642万
 $16,375/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -56198,7 +56182,7 @@
           <t>H | 385呎 (2房)
 $712万
 $18,501/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -56206,7 +56190,7 @@
           <t>J | 283呎 (1房)
 $478万
 $16,898/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -56238,7 +56222,7 @@
           <t>N | 383呎 (2房)
 $634万
 $16,564/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="O29" s="22" t="inlineStr">
@@ -56246,7 +56230,7 @@
           <t>P | 383呎 (2房)
 $634万
 $16,564/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="P29" s="22" t="inlineStr">
@@ -56254,7 +56238,7 @@
           <t>Q | 443呎 (2房)
 $797万
 $18,000/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8565,7 +8565,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -31555,7 +31555,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -31617,7 +31617,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -50035,7 +50035,7 @@
           <t>D | 383呎 (2房)
 $918万
 $23,979/呎
-(26年-07月-17日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -53288,7 +53288,7 @@
           <t>F | 262呎 (1房)
 $656万
 $25,031/呎
-(26年-07月-16日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
@@ -53296,7 +53296,7 @@
           <t>G | 392呎 (2房)
 $964万
 $24,589/呎
-(26年-07月-27日)</t>
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -30631,7 +30631,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -53161,7 +53161,7 @@
           <t>F | 262呎 (1房)
 $672万
 $25,656/呎
-(26年-07月-17日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -31361,7 +31361,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -53320,7 +53320,7 @@
           <t>K | 393呎 (2房)
 $961万
 $24,458/呎
-(26年-07月-20日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -9225,7 +9225,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -50186,7 +50186,7 @@
           <t>J | 287呎 (1房)
 $690万
 $24,052/呎
-(26年-07月-28日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="K13" s="22" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8242,34 +8242,34 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>8587000</v>
+        <v>7041000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>29920</v>
+        <v>24533</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="5" t="n">
-        <v>7041340</v>
+        <v>7041000</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>24534</v>
+        <v>24533</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="3" t="inlineStr">
@@ -32326,38 +32326,30 @@
       </c>
       <c r="F488" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H488" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I488" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="H488" s="5" t="n">
+        <v>9333000</v>
+      </c>
+      <c r="I488" s="5" t="n">
+        <v>23748</v>
       </c>
       <c r="J488" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K488" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L488" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K488" s="5" t="n">
+        <v>9333000</v>
+      </c>
+      <c r="L488" s="5" t="n">
+        <v>23748</v>
       </c>
       <c r="M488" s="3" t="inlineStr">
         <is>
@@ -32366,7 +32358,7 @@
       </c>
       <c r="N488" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -48989,7 +48981,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48999,7 +48991,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50054,12 +50046,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>J | 287呎 (1房)
-$859万
-$29,920/呎
-(在售)</t>
+$704万
+$24,533/呎
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -52353,7 +52345,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -52363,7 +52355,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -53426,12 +53418,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>K | 393呎 (2房)
-招标单位
--
-(在售)</t>
+$933万
+$23,748/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -9988,34 +9988,34 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>10587000</v>
+        <v>8454000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>26803</v>
+        <v>21403</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>8681340</v>
+        <v>8454000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>21978</v>
+        <v>21403</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -33904,7 +33904,7 @@
         </is>
       </c>
       <c r="E513" s="4" t="n">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>9624000</v>
       </c>
       <c r="I513" s="5" t="n">
-        <v>21725</v>
+        <v>21774</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>9624000</v>
       </c>
       <c r="L513" s="5" t="n">
-        <v>21725</v>
+        <v>21774</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
@@ -42013,14 +42013,14 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H643" s="5" t="n">
-        <v>6667000</v>
+        <v>6393000</v>
       </c>
       <c r="I643" s="5" t="n">
-        <v>17407</v>
+        <v>16692</v>
       </c>
       <c r="J643" s="3" t="inlineStr">
         <is>
@@ -42028,10 +42028,10 @@
         </is>
       </c>
       <c r="K643" s="5" t="n">
-        <v>6667000</v>
+        <v>6393000</v>
       </c>
       <c r="L643" s="5" t="n">
-        <v>17407</v>
+        <v>16692</v>
       </c>
       <c r="M643" s="3" t="inlineStr">
         <is>
@@ -48986,12 +48986,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50324,12 +50324,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M14" s="21" t="inlineStr">
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>M | 395呎 (2房)
-$1059万
-$26,803/呎
-(已定价未售)</t>
+$845万
+$21,403/呎
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -53714,9 +53714,9 @@
       </c>
       <c r="P14" s="23" t="inlineStr">
         <is>
-          <t>Q | 443呎 (2房)
+          <t>Q | 442呎 (2房)
 $962万
-$21,725/呎
+$21,774/呎
 (26年-07月-16日)</t>
         </is>
       </c>
@@ -54651,9 +54651,9 @@
       <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 383呎 (2房)
-$667万
-$17,407/呎
-(25年-11月-11日)</t>
+$639万
+$16,692/呎
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -7458,34 +7458,34 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>7921000</v>
+        <v>6495000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>30233</v>
+        <v>24790</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="5" t="n">
-        <v>6495220</v>
+        <v>6495000</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>24791</v>
+        <v>24790</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="3" t="inlineStr">
@@ -42013,14 +42013,14 @@
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H643" s="5" t="n">
-        <v>6393000</v>
+        <v>6667000</v>
       </c>
       <c r="I643" s="5" t="n">
-        <v>16692</v>
+        <v>17407</v>
       </c>
       <c r="J643" s="3" t="inlineStr">
         <is>
@@ -42028,10 +42028,10 @@
         </is>
       </c>
       <c r="K643" s="5" t="n">
-        <v>6393000</v>
+        <v>6667000</v>
       </c>
       <c r="L643" s="5" t="n">
-        <v>16692</v>
+        <v>17407</v>
       </c>
       <c r="M643" s="3" t="inlineStr">
         <is>
@@ -48981,7 +48981,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48991,7 +48991,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -49895,12 +49895,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
-$792万
-$30,233/呎
-(在售)</t>
+$650万
+$24,790/呎
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -54651,9 +54651,9 @@
       <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 383呎 (2房)
-$639万
-$16,692/呎
-(24年-10月-18日)</t>
+$667万
+$17,407/呎
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
